--- a/src/scrapers/output_scrape/sa/requirements_sa.xlsx
+++ b/src/scrapers/output_scrape/sa/requirements_sa.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,52 +433,58 @@
   </sheetPr>
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>state code</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>state stream</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>requirements</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Detail Requirements</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>service fee</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="225" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Skilled_Employment_in_South_Australia</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>ELIGIBILITY GUIDELINES
-- Have an active Expression of Interest (EOI) on the Department of Home Affairs’ SkillSelect system with South Australia as your first preferred State or Territory.
-- Check if your nominated occupation is eligible under the Skilled Employment in South Australia stream on South Australia’s Skilled Occupation List
+- Have an active Expression of Interest (EOI) on the Department of Home Affairs' SkillSelect system with South Australia as your first preferred State or Territory.
+- Check if your nominated occupation is eligible under the Skilled Employment in South Australia stream on South Australia's Skilled Occupation List
 - Currently live and work in South Australia
 - Be under 45 years of age at time of state nomination is approved
 - Have a valid and positive skills assessment for your nominated occupation
-- Have at least Competent English . To prove you have Competent English , you need to show evidence of an English approved test and score, or be a citizen of, and hold a valid passport from Canada, New Zealand, the Republic of Ireland, the United Kingdom of Great Britain and Northern Ireland, or the United States of America. Note that if you hold a valid passport from any of these countries and would like to claim higher levels of English proficiency on your EOI, you must show evidence of an English approved test and score.
-- Score at least 65 points in the Department of Home Affairs’ points test (including state nomination points)
+- Have at least Competent English . To prove you have Competent English , you need to show evidence of an English approved test and score, or be a citizen of, and hold a valid passport from Canada, New Zealand, the Republic of Ireland, the United Kingdom of Great Britain and Northern Ireland, or the United States of America. Note that if you hold a valid passport from any of these countries and would like to claim higher levels of English proficiency on your EOI, you must show evidence of an English approved test and score.
+- Score at least 65 points in the Department of Home Affairs' points test (including state nomination points)
 - Have been residing in South Australia for at least the last 12 months
-- Have been working for the last 12 months, and be currently employed, in a full-time (at least 30 hours per week) job. Your job must be related to, and at the same skill level as, your nominated occupation. For South Australian nomination, this is generally defined as being in the same Australian and New Zealand Standard Classification of Occupations (ANZSCO) Sub Major Group (represented by the first two digits of the ANZSCO code).
+- Have been working for the last 12 months, and be currently employed, in a full-time (at least 30 hours per week) job. Your job must be related to, and at the same skill level as, your nominated occupation. For South Australian nomination, this is generally defined as being in the same Australian and New Zealand Standard Classification of Occupations (ANZSCO) Sub Major Group (represented by the first two digits of the ANZSCO code).
 - English language proficiency
 - Years of skilled experience in your nominated occupation
 - Skills and qualifications level
@@ -468,40 +492,40 @@
 - Assessment of employer.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="315" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>South_Australian_Graduates</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>ELIGIBILITY GUIDELINES
-- Have an active Expression of Interest (EOI) on the Department of Home Affairs’ SkillSelect system with South Australia as your first preferred State or Territory.
-- Check if your nominated occupation is eligible under the South Australian Graduates stream on South Australia’s Skilled Occupation List
+- Have an active Expression of Interest (EOI) on the Department of Home Affairs' SkillSelect system with South Australia as your first preferred State or Territory.
+- Check if your nominated occupation is eligible under the South Australian Graduates stream on South Australia's Skilled Occupation List
 - Currently live and work in South Australia
 - Be under 45 years of age at the time your state nomination is approved
 - Have a valid and positive skills assessment for your nominated occupation
 - Have at least Competent English . To prove you have Competent English , you need to show evidence of an English approved test and score, or be a citizen of, and hold a valid passport from Canada, New Zealand, the Republic of Ireland, the United Kingdom of Great Britain and Northern Ireland, or the United States of America. Note that if you hold a valid passport from any of these countries and would like to claim higher levels of English proficiency on your EOI, you must show evidence of an English approved test and score.
-- Score at least 65 points in the Department of Home Affairs’ points test (including state nomination points)
+- Score at least 65 points in the Department of Home Affairs' points test (including state nomination points)
 - Have completed your qualification at a South Australian education provider and meet the following study requirements: Your course in South Australia must be Commonwealth Register of Institutions and Courses for Overseas Students (CRICOS) registered, with a minimum of 46 CRICOS week. Your study meets the minimum qualification level listed for your nominated occupation on the Skilled Occupation List A minimum of 75% of your qualification must have been completed in South Australia You must have resided in South Australia for at least one year during your studies
 - Your course in South Australia must be Commonwealth Register of Institutions and Courses for Overseas Students (CRICOS) registered, with a minimum of 46 CRICOS week.
 - Your study meets the minimum qualification level listed for your nominated occupation on the Skilled Occupation List
 - A minimum of 75% of your qualification must have been completed in South Australia
 - You must have resided in South Australia for at least one year during your studies
 - Have been residing in South Australia for at least the last 6 months
-- Have been working full-time for the last 6 months, and be currently employed full-time (at least 30 hours per week). Your job must be related to, and at the same Australian and New Zealand Standard Classification of Occupations (ANZSCO) Sub Major Group (represented by the first two digits of the ANZSCO code).
+- Have been working full-time for the last 6 months, and be currently employed full-time (at least 30 hours per week). Your job must be related to, and at the same Australian and New Zealand Standard Classification of Occupations (ANZSCO) Sub Major Group (represented by the first two digits of the ANZSCO code).
 - Have undertaken your skilled work experience post-course completion.
 - English language proficiency
 - Years of skilled experience in your nominated occupation
@@ -510,28 +534,28 @@
 - Assessment of employer.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="150" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Outer_Regional_Skilled_Employment</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>ELIGIBILITY GUIDELINES
 - Have an active Expression of Interest (EOI) in the Department of Home Affairs SkillSelect system, with South Australia selected as your first preferred state or territory.
-- Confirm your nominated occupation is eligible under the Outer Regional Skilled Employment stream on South Australia’s Skilled Occupation List .
+- Confirm your nominated occupation is eligible under the Outer Regional Skilled Employment stream on South Australia's Skilled Occupation List .
 - Currently live and work in Outer Regional South Australia .
 - Be under 45 years of age at the time state nomination is approved.
 - Hold a valid and positive skills assessment for your nominated occupation
@@ -541,42 +565,42 @@
 - Your employment must be related to, and at the same skill level as, your nominated occupation. For South Australian nomination, this is generally defined as being within the same Australian and New Zealand Standard Classification of Occupations (ANZSCO) Sub Major Group, represented by the first two digits of the ANZSCO code.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="255" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Moving_to_South_Australia_from_Overseas</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>SUBMIT AN EXPRESSION OF INTEREST (EOI)
-  Create an EOI in the SkillSelect system and choose South Australia as your first preferred state or territory.
-  Please note that if you are applying from outside Australia, you do not need to submit a Registration of Interest (ROI) via the Skilled &amp; Business Migration portal. This step only applies to onshore or specific streams.
+ Create an EOI in the SkillSelect system and choose South Australia as your first preferred state or territory.
+ Please note that if you are applying from outside Australia, you do not need to submit a Registration of Interest (ROI) via the Skilled &amp; Business Migration portal. This step only applies to onshore or specific streams.
 CHECK YOUR ELIGIBILITY
-  To be considered for South Australian nomination, you must:
+ To be considered for South Australian nomination, you must:
 - Have at least three years of skilled work experience in your nominated or closely related occupation (within the last 5 years)
 - Meet the visa requirements set by the Department of Home Affairs
 - Your application must demonstrate that you were eligible for the claims entered in your SkillSelect EOI at the time of invitation
-- Meet South Australia’s state nomination requirements
+- Meet South Australia's state nomination requirements
 UNDERSTAND HOW YOU'LL BE ASSESSED
-  Your application is assessed by merit on the following factors:
-  *Work experience must be in a role deemed full-time, defined as 20 hours per week according to SkillSelect.
+ Your application is assessed by merit on the following factors:
+ *Work experience must be in a role deemed full-time, defined as 20 hours per week according to SkillSelect.
 WAIT FOR AN INVITATION
-  If selected, you’ll be invited to apply for South Australian state nomination. You will then have 14 days to submit your application, so make sure your EOI details are accurate and up to date.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+ If selected, you'll be invited to apply for South Australian state nomination. You will then have 14 days to submit your application, so make sure your EOI details are accurate and up to date.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/src/scrapers/output_scrape/sa/requirements_sa.xlsx
+++ b/src/scrapers/output_scrape/sa/requirements_sa.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,24 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -441,39 +426,39 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>state code</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>state stream</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Detail Requirements</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>service fee</t>
         </is>
       </c>
     </row>
     <row r="2" ht="225" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Skilled_Employment_in_South_Australia</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>ELIGIBILITY GUIDELINES
 - Have an active Expression of Interest (EOI) on the Department of Home Affairs' SkillSelect system with South Australia as your first preferred State or Territory.
@@ -492,24 +477,24 @@
 - Assessment of employer.</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="3" ht="315" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>South_Australian_Graduates</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>ELIGIBILITY GUIDELINES
 - Have an active Expression of Interest (EOI) on the Department of Home Affairs' SkillSelect system with South Australia as your first preferred State or Territory.
@@ -534,24 +519,24 @@
 - Assessment of employer.</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Outer_Regional_Skilled_Employment</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>ELIGIBILITY GUIDELINES
 - Have an active Expression of Interest (EOI) in the Department of Home Affairs SkillSelect system, with South Australia selected as your first preferred state or territory.
@@ -565,24 +550,24 @@
 - Your employment must be related to, and at the same skill level as, your nominated occupation. For South Australian nomination, this is generally defined as being within the same Australian and New Zealand Standard Classification of Occupations (ANZSCO) Sub Major Group, represented by the first two digits of the ANZSCO code.</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="5" ht="255" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>Moving_to_South_Australia_from_Overseas</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>SUBMIT AN EXPRESSION OF INTEREST (EOI)
  Create an EOI in the SkillSelect system and choose South Australia as your first preferred state or territory.
@@ -600,7 +585,7 @@
  If selected, you'll be invited to apply for South Australian state nomination. You will then have 14 days to submit your application, so make sure your EOI details are accurate and up to date.</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/src/scrapers/output_scrape/sa/requirements_sa.xlsx
+++ b/src/scrapers/output_scrape/sa/requirements_sa.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -426,39 +441,39 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>state code</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>state stream</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Detail Requirements</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>service fee</t>
         </is>
       </c>
     </row>
     <row r="2" ht="225" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Skilled_Employment_in_South_Australia</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>ELIGIBILITY GUIDELINES
 - Have an active Expression of Interest (EOI) on the Department of Home Affairs' SkillSelect system with South Australia as your first preferred State or Territory.
@@ -477,24 +492,24 @@
 - Assessment of employer.</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="3" ht="315" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>South_Australian_Graduates</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>ELIGIBILITY GUIDELINES
 - Have an active Expression of Interest (EOI) on the Department of Home Affairs' SkillSelect system with South Australia as your first preferred State or Territory.
@@ -519,24 +534,24 @@
 - Assessment of employer.</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Outer_Regional_Skilled_Employment</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>ELIGIBILITY GUIDELINES
 - Have an active Expression of Interest (EOI) in the Department of Home Affairs SkillSelect system, with South Australia selected as your first preferred state or territory.
@@ -550,24 +565,24 @@
 - Your employment must be related to, and at the same skill level as, your nominated occupation. For South Australian nomination, this is generally defined as being within the same Australian and New Zealand Standard Classification of Occupations (ANZSCO) Sub Major Group, represented by the first two digits of the ANZSCO code.</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="5" ht="255" customHeight="1">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Moving_to_South_Australia_from_Overseas</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>SUBMIT AN EXPRESSION OF INTEREST (EOI)
  Create an EOI in the SkillSelect system and choose South Australia as your first preferred state or territory.
@@ -585,7 +600,7 @@
  If selected, you'll be invited to apply for South Australian state nomination. You will then have 14 days to submit your application, so make sure your EOI details are accurate and up to date.</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
